--- a/resource/OrangeHRM_Manual_TestCases.xlsx
+++ b/resource/OrangeHRM_Manual_TestCases.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leave" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recruitment" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -591,6 +592,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -741,198 +743,238 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B12" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2. Chú thích Severity (mức độ nghiêm trọng — S cao nhất → D thấp nhất)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Showstopper — Lỗi chặn toàn bộ, hệ thống không dùng được (crash, không login, mất dữ liệu)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Critical — Chức năng chính lỗi nghiêm trọng, không có workaround</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Major — Chức năng lỗi nhưng có workaround, ảnh hưởng đáng kể</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Minor — Lỗi nhỏ, ít ảnh hưởng chức năng chính</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Cosmetic — Lỗi giao diện/thẩm mỹ, không ảnh hưởng chức năng</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>3. Chú thích Priority (mức độ ưu tiên thực thi test)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Phải test đầu tiên — luồng nghiệp vụ cốt lõi, bảo mật</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Ưu tiên cao — chức năng quan trọng, validation chính</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Ưu tiên trung bình — chức năng phụ trợ, filter, edge case</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Ưu tiên thấp — trường hợp hiếm, cosmetic, boundary xa</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>4. Phân công bài tập về nhà (mỗi người 1 module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Người 1</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>PIM (Employee) — sheet PIM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Người 2</t>
+          <t>Người 1</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Admin (User Management) — sheet Admin</t>
+          <t>PIM (Employee) — sheet PIM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Người 3</t>
+          <t>Người 2</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Leave (Apply/Assign) — sheet Leave</t>
+          <t>Admin (User Management) — sheet Admin</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>Người 3</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Leave (Apply/Assign) — sheet Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>Người 4</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Recruitment (Candidates/Vacancies) — sheet Recruitment</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Người 5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Time (Timesheets / Attendance) — sheet Time</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B31:F31"/>
@@ -952,6 +994,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7097,4 +7140,1267 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>OrangeHRM — Time Module (Timesheets / Attendance) — Manual Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Site: https://opensource-demo.orangehrmlive.com  •  Tài khoản: Admin / admin123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Test Case Title</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Description (Step-by-step)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC01</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Tạo Timesheet mới cho tuần hiện tại</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>1. Login
+2. Vào Time &gt; Timesheets &gt; My Timesheets
+3. Click Create Timesheet cho tuần chưa có
+4. Xác nhận</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>(tuần hiện tại chưa có timesheet)</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Timesheet tuần được tạo, hiển thị lưới nhập giờ theo ngày</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Luồng chính module Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC02</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Nhập giờ làm việc vào Timesheet</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>1. Mở My Timesheet
+2. Chọn Project và Activity
+3. Nhập số giờ cho từng ngày
+4. Click Save</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Project=(chọn), Activity=(chọn), Mon=8, Tue=8</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Giờ được lưu, tổng giờ (Total) cập nhật đúng</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>Nhập dữ liệu cốt lõi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC03</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Submit Timesheet để duyệt</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>1. Nhập đủ giờ trong tuần
+2. Click Submit</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>(timesheet đã nhập giờ)</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Timesheet chuyển trạng thái 'Submitted', chờ duyệt</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Luồng submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC04</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Nhập giờ chứa ký tự chữ</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>1. Mở timesheet
+2. Nhập chữ cái vào ô giờ
+3. Save</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Giờ=abc</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi định dạng, không lưu giá trị sai</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Validation định dạng số</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC05</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Nhập giờ vượt quá 24h/ngày</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>1. Mở timesheet
+2. Nhập giá trị &gt;24 vào 1 ngày
+3. Save</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Giờ=30</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Xác nhận hành vi: cảnh báo hoặc chặn — ghi nhận thực tế</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>Kiểm tra ràng buộc logic giờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC06</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Nhập giờ định dạng HH:MM</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>1. Mở timesheet
+2. Nhập giờ dạng 08:30
+3. Save</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Giờ=08:30</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Hệ thống chấp nhận định dạng giờ:phút, tính tổng đúng</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>Kiểm tra định dạng giờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC07</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Submit Timesheet chưa nhập giờ</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>1. Tạo timesheet trống
+2. Click Submit ngay</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>(timesheet rỗng)</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Xác nhận hành vi: cho submit rỗng hoặc cảnh báo — ghi nhận thực tế</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Edge case submit rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC08</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Xem Timesheet của kỳ trước</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>1. Vào My Timesheets
+2. Điều hướng về tuần trước bằng nút Previous</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>(click Previous period)</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Hiển thị timesheet đúng của kỳ trước</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Điều hướng kỳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC09</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Approve Timesheet (role duyệt)</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>1. Login role supervisor
+2. Vào Time &gt; Timesheets &gt; Employee Timesheets
+3. Mở timesheet Submitted
+4. Click Approve</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>(timesheet đang Submitted)</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Timesheet chuyển trạng thái 'Approved'</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Luồng phê duyệt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC10</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Reject Timesheet</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>1. Mở Employee Timesheet đang Submitted
+2. Click Reject
+3. Nhập lý do</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>(timesheet Submitted)</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Timesheet chuyển 'Rejected', lưu lý do</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>Luồng từ chối</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC11</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Search Employee Timesheet theo tên</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>1. Vào Employee Timesheets
+2. Nhập tên nhân viên
+3. Click View</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Employee Name=John Doe</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Hiển thị timesheet của nhân viên khớp tên</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>Tìm kiếm timesheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC12</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Search Timesheet nhân viên không tồn tại</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>1. Vào Employee Timesheets
+2. Nhập tên không tồn tại
+3. View</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Employee Name=ZZZNotExist</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi Invalid hoặc No Records</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>Kết quả rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC13</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Punch In (Attendance)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>1. Vào Time &gt; Attendance &gt; Punch In/Out
+2. Nhập ghi chú (tùy chọn)
+3. Click In</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Note=Bắt đầu ca</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Ghi nhận thời điểm Punch In, hiển thị trạng thái đang làm việc</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>Chấm công vào</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC14</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Punch Out (Attendance)</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>1. Sau khi đã Punch In
+2. Vào Punch In/Out
+3. Click Out</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>(đã Punch In trước đó)</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>Ghi nhận thời điểm Punch Out, tính thời lượng ca làm</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>Chấm công ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC15</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Punch Out khi chưa Punch In</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>1. Chưa Punch In
+2. Vào Punch In/Out</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>(chưa punch in)</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Chỉ hiển thị nút Punch In, không cho Punch Out</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>Ràng buộc logic chấm công</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC16</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Punch In hai lần liên tiếp</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>1. Punch In
+2. Thử Punch In lần nữa mà chưa Out</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>(đã punch in)</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Không cho Punch In lại, chỉ hiển thị nút Punch Out</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>Ràng buộc trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC17</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Sửa thời gian Punch (Edit)</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>1. Vào Attendance &gt; My Records
+2. Chọn 1 bản ghi
+3. Sửa giờ
+4. Save</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>(bản ghi có sẵn)</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Thời gian được cập nhật, thời lượng tính lại đúng</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>Chỉnh sửa chấm công</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC18</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Xem Attendance Records theo ngày</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>1. Vào Attendance &gt; Employee Records
+2. Chọn nhân viên và ngày
+3. View</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Employee=John, Date=hôm nay</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Hiển thị bản ghi chấm công của ngày đã chọn</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>Xem lịch sử chấm công</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC19</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Punch In với ghi chú Unicode/tiếng Việt</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>1. Punch In
+2. Nhập ghi chú tiếng Việt có dấu
+3. In</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Note=Ca sáng thứ hai</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Ghi chú lưu đúng, không lỗi encoding</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>Kiểm tra Unicode</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC20</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Cấu hình Project Info (Customers)</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>1. Vào Time &gt; Project Info &gt; Customers &gt; Add
+2. Nhập tên customer
+3. Save</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Customer Name=ABC Corp</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Customer mới được thêm vào danh sách</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>Cấu hình dự án</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC21</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Thêm Project mới</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>1. Vào Project Info &gt; Projects &gt; Add
+2. Nhập tên, chọn Customer
+3. Save</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Project=Website Redesign, Customer=ABC Corp</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Project mới được tạo</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>Quản lý project</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC22</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>Thêm Project — bỏ trống tên</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>1. Add Project
+2. Để trống Project Name
+3. Save</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Project Name=(rỗng)</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi 'Required'</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I26" s="19" t="inlineStr">
+        <is>
+          <t>Validation bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>TIME_TC23</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Reset filter Employee Timesheets</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>1. Nhập filter
+2. Click Reset</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>(sau khi filter)</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Xóa trắng filter tìm kiếm</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>Chức năng Reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>TIME_TC24</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Truy cập Employee Timesheets bằng user ESS</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>1. Login user ESS
+2. Thử truy cập Employee Timesheets của người khác</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>(user role ESS)</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Không cho xem timesheet người khác, chỉ xem của mình</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>Kiểm tra phân quyền RBAC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>